--- a/output/pdf_financials_xlsx/ABA.xlsx
+++ b/output/pdf_financials_xlsx/ABA.xlsx
@@ -892,19 +892,19 @@
         <v>-0.06598999999999999</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.025826</v>
+        <v>-0.025826</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>8.093476000000001</v>
+        <v>-8.093476000000001</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2.406875</v>
+        <v>-2.406875</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>6.462896</v>
+        <v>-6.462896</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>5.547677</v>
+        <v>-5.547677</v>
       </c>
     </row>
     <row r="17">
@@ -1048,19 +1048,19 @@
         <v>-0.06598999999999999</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.025826</v>
+        <v>-0.025826</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>8.093476000000001</v>
+        <v>-8.093476000000001</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2.406875</v>
+        <v>-2.406875</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>6.462896</v>
+        <v>-6.462896</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>5.547677</v>
+        <v>-5.547677</v>
       </c>
     </row>
     <row r="21">
@@ -1141,19 +1141,19 @@
         <v>-0.06598999999999999</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.025826</v>
+        <v>-0.025826</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>8.093476000000001</v>
+        <v>-8.093476000000001</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>2.406875</v>
+        <v>-2.406875</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>6.462896</v>
+        <v>-6.462896</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>5.547677</v>
+        <v>-5.547677</v>
       </c>
     </row>
     <row r="24">
@@ -1241,16 +1241,16 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>32.373904</v>
+        <v>-32.373904</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>48.1375</v>
+        <v>-48.1375</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>80.78619999999999</v>
+        <v>-80.78619999999999</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>110.95354</v>
+        <v>-110.95354</v>
       </c>
     </row>
     <row r="27">
@@ -1269,19 +1269,19 @@
         <v>-0.06598999999999999</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.025826</v>
+        <v>-0.025826</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>8.093476000000001</v>
+        <v>-8.093476000000001</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>2.406875</v>
+        <v>-2.406875</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>6.462896</v>
+        <v>-6.462896</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>5.547677</v>
+        <v>-5.547677</v>
       </c>
     </row>
     <row r="28">
@@ -1331,19 +1331,19 @@
         <v>-0.06598999999999999</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.025826</v>
+        <v>-0.025826</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>8.099987</v>
+        <v>-8.086964999999999</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>2.429578</v>
+        <v>-2.384172</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>6.462896</v>
+        <v>-6.462896</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>5.547677</v>
+        <v>-5.547677</v>
       </c>
     </row>
     <row r="30">
@@ -1409,19 +1409,19 @@
         <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -3329,22 +3329,22 @@
         <v>0.210071</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.1225</v>
+        <v>0.210071</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0.1225</v>
+        <v>0.191187</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.1225</v>
+        <v>1.907152</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.162417</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.263379</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.010543</v>
       </c>
     </row>
     <row r="93">
@@ -5194,7 +5194,11 @@
           <t>Reserves (notes 9 and 10)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -5680,7 +5684,11 @@
           <t>Reserves (notes 8 and 9)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -6354,7 +6362,11 @@
           <t>Reserves (Notes 9, 10)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -10328,10 +10340,10 @@
         </is>
       </c>
       <c r="K104" s="5" t="n">
-        <v>6.462896</v>
+        <v>-6.462896</v>
       </c>
       <c r="L104" s="5" t="n">
-        <v>5.547677</v>
+        <v>-5.547677</v>
       </c>
     </row>
     <row r="105">
@@ -12239,7 +12251,7 @@
         </is>
       </c>
       <c r="J138" s="5" t="n">
-        <v>2.406875</v>
+        <v>-2.406875</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
@@ -13696,10 +13708,10 @@
         </is>
       </c>
       <c r="I164" s="5" t="n">
-        <v>8.093476000000001</v>
+        <v>-8.093476000000001</v>
       </c>
       <c r="J164" s="5" t="n">
-        <v>2.406875</v>
+        <v>-2.406875</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
@@ -15271,10 +15283,10 @@
         </is>
       </c>
       <c r="H192" s="5" t="n">
-        <v>0.025826</v>
+        <v>-0.025826</v>
       </c>
       <c r="I192" s="5" t="n">
-        <v>5.515211</v>
+        <v>-5.515211</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ABA.xlsx
+++ b/output/pdf_financials_xlsx/ABA.xlsx
@@ -771,16 +771,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.032593</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.053395</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.069105</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.024142</v>
       </c>
     </row>
     <row r="13">
@@ -1272,16 +1272,16 @@
         <v>-0.025826</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-8.093476000000001</v>
+        <v>-8.060883</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.406875</v>
+        <v>-2.35348</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-6.462896</v>
+        <v>-6.393791</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-5.547677</v>
+        <v>-5.523535</v>
       </c>
     </row>
     <row r="28">
@@ -1334,16 +1334,16 @@
         <v>-0.025826</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-8.086964999999999</v>
+        <v>-8.054372000000001</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.384172</v>
+        <v>-2.330777</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-6.462896</v>
+        <v>-6.393791</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-5.547677</v>
+        <v>-5.523535</v>
       </c>
     </row>
     <row r="30">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.127839</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.184557</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.0956</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.100655</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.53046</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.705619</v>
@@ -1506,7 +1506,7 @@
         <v>1.130468</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.498646</v>
       </c>
     </row>
     <row r="35">
@@ -1547,19 +1547,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.127839</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.184557</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.0956</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.100655</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.53046</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0.705619</v>
@@ -1568,7 +1568,7 @@
         <v>1.130468</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.498646</v>
       </c>
     </row>
     <row r="37">
@@ -1919,19 +1919,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.13406</v>
+        <v>0.006221</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.186205</v>
+        <v>0.001648</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.09640799999999999</v>
+        <v>0.000808</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.102758</v>
+        <v>0.002103</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.687981</v>
+        <v>0.157521</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.163464</v>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -13516,7 +13516,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -15092,7 +15092,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">

--- a/output/pdf_financials_xlsx/ABA.xlsx
+++ b/output/pdf_financials_xlsx/ABA.xlsx
@@ -4687,7 +4687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L204"/>
+  <dimension ref="A1:L221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7474,7 +7474,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E52" s="5" t="n">
         <v>0.2025</v>
       </c>
@@ -7980,21 +7984,13 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Items not affecting cash</t>
-        </is>
-      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>FOR THE YEARS ENDED APRIL</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -8015,11 +8011,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I62" s="5" t="n">
-        <v>0.006511</v>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J62" s="5" t="n">
-        <v>0.022703</v>
+        <v>3e-05</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -8040,12 +8038,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Listing expenses</t>
+          <t>Loss for the year $ (6,462,896) $</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -8069,13 +8067,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="5" t="n">
-        <v>5.201969</v>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="n">
+        <v>-2.406875</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -8096,15 +8094,19 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cash acquired in the transaction</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>Amortization 26,044</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -8125,13 +8127,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="5" t="n">
-        <v>0.011724</v>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="n">
+        <v>0.022703</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -8152,19 +8154,15 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Purchase of property and equipment</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>PurchaseOfPPE</t>
-        </is>
-      </c>
+          <t>Flow-through shares premium (871,250)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -8185,13 +8183,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="5" t="n">
-        <v>-0.078125</v>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="n">
+        <v>-0.554491</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -8212,24 +8210,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cash used in investing activities</t>
+          <t>Share-based compensation 414,800</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="n">
-        <v>-0.04595</v>
-      </c>
-      <c r="F66" s="5" t="n">
-        <v>-0.100911</v>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -8241,8 +8243,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="5" t="n">
-        <v>-0.196665</v>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -8268,12 +8272,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Changes in non-cash working capital balances</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Investment by parent through the arrangement date</t>
+          <t>Accounts receivable and prepaid expenses (192,423)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -8297,13 +8301,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="5" t="n">
-        <v>0.467647</v>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="n">
+        <v>-0.005943</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -8324,15 +8328,19 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SUPPLEMENTAL INFORMATION</t>
+          <t>Changes in non-cash working capital balances</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Consideration issued in arrangement</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities 546,113</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -8353,13 +8361,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="5" t="n">
-        <v>4.577978</v>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="n">
+        <v>-0.103954</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -8380,12 +8388,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SUPPLEMENTAL INFORMATION</t>
+          <t>Changes in non-cash working capital balances</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Shares issued in the arrangement</t>
+          <t>Cash used in operating activities (6,539,612)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -8409,13 +8417,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="5" t="n">
-        <v>0.542933</v>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="n">
+        <v>-3.04856</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -8436,12 +8444,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Common shares issued for mineral property</t>
+          <t>Private placements - cash 7,100,000</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -8465,13 +8473,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="5" t="n">
-        <v>2.563929</v>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="n">
+        <v>2.25</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -8492,19 +8500,15 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital balances</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Amounts receivable and prepaid expenses</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
+          <t>Private placements - issue costs (135,539)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -8520,16 +8524,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H71" s="5" t="n">
-        <v>-0.001295</v>
-      </c>
-      <c r="I71" s="5" t="n">
-        <v>-0.155418</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="n">
+        <v>-0.026281</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -8555,10 +8561,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Shares issued for cash (net of issue costs)</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>Cash provided by financing activities 6,964,461</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -8574,16 +8584,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H72" s="5" t="n">
-        <v>0.031964</v>
-      </c>
-      <c r="I72" s="5" t="n">
-        <v>3.6329</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="n">
+        <v>2.223719</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -8604,15 +8616,19 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SUPPLEMENTAL INFORMATION</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Shares issued for mineral property $</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>CHANGE IN CASH DURING THE YEAR 424,849</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -8633,13 +8649,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="5" t="n">
-        <v>2.563929</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="n">
+        <v>-0.824841</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -8660,40 +8676,46 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Net loss for the year $</t>
+          <t>CASH, BEGINNING OF THE YEAR 705,619</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="n">
-        <v>-0.146244</v>
-      </c>
-      <c r="F74" s="5" t="n">
-        <v>-0.214176</v>
-      </c>
-      <c r="G74" s="5" t="n">
-        <v>-0.06598999999999999</v>
-      </c>
-      <c r="H74" s="5" t="n">
-        <v>-0.053709</v>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J74" s="5" t="n">
+        <v>1.53046</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -8714,24 +8736,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Share-based payment</t>
+          <t>CASH, END OF THE YEAR $ 1,130,468 $</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="n">
-        <v>0.1225</v>
-      </c>
-      <c r="F75" s="5" t="n">
-        <v>0.068666</v>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -8748,10 +8774,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J75" s="5" t="n">
+        <v>0.705619</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -8772,26 +8796,34 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>SUPPLEMENTAL INFORMATION</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Amounts recoverable</t>
+          <t>Finders' warrants issued $ 18,300 $</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" s="5" t="n">
-        <v>-0.002422</v>
-      </c>
-      <c r="F76" s="5" t="n">
-        <v>0.004573</v>
-      </c>
-      <c r="G76" s="5" t="n">
-        <v>0.00084</v>
-      </c>
-      <c r="H76" s="5" t="n">
-        <v>-0.001295</v>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -8822,36 +8854,42 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>SUPPLEMENTAL INFORMATION</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued expenses</t>
+          <t>Warrants issued 1,623,980</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" s="5" t="n">
-        <v>-0.002545</v>
-      </c>
-      <c r="F77" s="5" t="n">
-        <v>0.026012</v>
-      </c>
-      <c r="G77" s="5" t="n">
-        <v>-0.023807</v>
-      </c>
-      <c r="H77" s="5" t="n">
-        <v>0.000212</v>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J77" s="5" t="n">
+        <v>0.26</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -8872,40 +8910,42 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>SUPPLEMENTAL INFORMATION</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cash used in operating activities</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="n">
-        <v>-0.028711</v>
-      </c>
-      <c r="F78" s="5" t="n">
-        <v>-0.114925</v>
-      </c>
-      <c r="G78" s="5" t="n">
-        <v>-0.08895699999999999</v>
-      </c>
-      <c r="H78" s="5" t="n">
-        <v>-0.054792</v>
+          <t>Interest received 69,105</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J78" s="5" t="n">
+        <v>0.053395</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -8926,15 +8966,19 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Mineral property tax credit</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -8950,18 +8994,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H79" s="5" t="n">
-        <v>0.027883</v>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>0.006511</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>0.022703</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -8982,35 +9024,37 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CHANGE IN CASH</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="n">
-        <v>0.127839</v>
-      </c>
-      <c r="F80" s="5" t="n">
-        <v>0.056718</v>
-      </c>
-      <c r="G80" s="5" t="n">
-        <v>-0.08895699999999999</v>
-      </c>
-      <c r="H80" s="5" t="n">
-        <v>0.005055</v>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Listing expenses</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>5.201969</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -9036,37 +9080,37 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CASH, BEGINNING OF YEAR</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Cash acquired in the transaction</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F81" s="5" t="n">
-        <v>0.127839</v>
-      </c>
-      <c r="G81" s="5" t="n">
-        <v>0.184557</v>
-      </c>
-      <c r="H81" s="5" t="n">
-        <v>0.0956</v>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>0.011724</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -9092,35 +9136,41 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CASH, END OF YEAR $</t>
+          <t>Purchase of property and equipment</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="n">
-        <v>0.127839</v>
-      </c>
-      <c r="F82" s="5" t="n">
-        <v>0.184557</v>
-      </c>
-      <c r="G82" s="5" t="n">
-        <v>0.0956</v>
-      </c>
-      <c r="H82" s="5" t="n">
-        <v>0.100655</v>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>-0.078125</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -9146,28 +9196,24 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SUPPLEMENTAL INFORMATION</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Interest and income taxes paid $</t>
+          <t>Cash used in investing activities</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>IncomeTaxPaidSupplementalData</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>-0.04595</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>-0.100911</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -9179,10 +9225,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I83" s="5" t="n">
+        <v>-0.196665</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -9208,12 +9252,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SUPPLEMENTAL INFORMATION</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Total $ 403,296 (65,990) 337,306 31,964</t>
+          <t>Investment by parent through the arrangement date</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -9227,16 +9271,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G84" s="5" t="n">
-        <v>0.315561</v>
-      </c>
-      <c r="H84" s="5" t="n">
-        <v>-0.053709</v>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>0.467647</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -9267,7 +9313,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Deficit $ (360,420) (65,990) (426,410) -</t>
+          <t>Consideration issued in arrangement</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -9281,16 +9327,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G85" s="5" t="n">
-        <v>-0.480119</v>
-      </c>
-      <c r="H85" s="5" t="n">
-        <v>-0.053709</v>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>4.577978</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -9316,12 +9364,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>$  -   -                                                                                                                                                                                                                      these</t>
+          <t>SUPPLEMENTAL INFORMATION</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>$  -   -                                                                                                                                                                                                                      these of Amount 553,645 553,645</t>
+          <t>Shares issued in the arrangement</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -9335,16 +9383,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G86" s="5" t="n">
-        <v>0.6044929999999999</v>
-      </c>
-      <c r="H86" s="5" t="n">
-        <v>0.050848</v>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>0.542933</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -9370,24 +9420,24 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Exploration and evaluation asset</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="n">
-        <v>-0.046151</v>
-      </c>
-      <c r="F87" s="5" t="n">
-        <v>-0.100911</v>
+          <t>Common shares issued for mineral property</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -9399,10 +9449,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I87" s="5" t="n">
+        <v>2.563929</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -9428,37 +9476,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Changes in non-cash working capital balances</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Payment of loan payable to related party</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
+          <t>Amounts receivable and prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F88" s="5" t="n">
-        <v>-0.012</v>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H88" s="5" t="n">
+        <v>-0.001295</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>-0.155418</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -9484,17 +9534,19 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Cash acquired on amalgamation with Pontiac Resources Corp.</t>
+          <t>Shares issued for cash (net of issue costs)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" s="5" t="n">
-        <v>0.000201</v>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9506,15 +9558,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H89" s="5" t="n">
+        <v>0.031964</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>3.6329</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -9545,14 +9593,10 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Interest and income taxes paid</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>IncomeTaxPaidSupplementalData</t>
-        </is>
-      </c>
+          <t>Shares issued for mineral property $</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -9573,10 +9617,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I90" s="5" t="n">
+        <v>2.563929</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -9602,30 +9644,30 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SUPPLEMENTAL INFORMATION</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Total $ - 200,000 85,496 2,500 122,500 (146,244) 264,252 400,000 (115,446) 68,666</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
+          <t>Net loss for the year $</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E91" s="5" t="n">
-        <v>0.403296</v>
+        <v>-0.146244</v>
       </c>
       <c r="F91" s="5" t="n">
         <v>-0.214176</v>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G91" s="5" t="n">
+        <v>-0.06598999999999999</v>
+      </c>
+      <c r="H91" s="5" t="n">
+        <v>-0.053709</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -9656,20 +9698,24 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SUPPLEMENTAL INFORMATION</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Deficit $ - - - - - (146,244) (146,244) - - -</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
+          <t>Share-based payment</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E92" s="5" t="n">
-        <v>-0.36042</v>
+        <v>0.1225</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>-0.214176</v>
+        <v>0.068666</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -9710,30 +9756,26 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>of</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>1 - - - - - part Common Shares integral of 4,000,000 2,000,000 2,500,000 8,500,001</t>
+          <t>Amounts recoverable</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" s="5" t="n">
-        <v>12.500001</v>
+        <v>-0.002422</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.004573</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>0.00084</v>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>-0.001295</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -9759,39 +9801,31 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Exploration expenses (notes 7, 11) $</t>
+          <t>Accounts payable and accrued expenses</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E94" s="5" t="n">
+        <v>-0.002545</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>0.026012</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>-0.023807</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>0.000212</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -9803,53 +9837,49 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K94" s="5" t="n">
-        <v>6.783447</v>
-      </c>
-      <c r="L94" s="5" t="n">
-        <v>8.62969</v>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>General administrative (note 11)</t>
+          <t>Cash used in operating activities</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>-0.028711</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>-0.114925</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>-0.08895699999999999</v>
+      </c>
+      <c r="H95" s="5" t="n">
+        <v>-0.054792</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -9861,27 +9891,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K95" s="5" t="n">
-        <v>0.010864</v>
-      </c>
-      <c r="L95" s="5" t="n">
-        <v>0.023994</v>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Investor relations and promotion</t>
+          <t>Mineral property tax credit</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -9900,60 +9934,62 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I96" s="5" t="n">
-        <v>0.018635</v>
-      </c>
-      <c r="J96" s="5" t="n">
-        <v>0.038311</v>
-      </c>
-      <c r="K96" s="5" t="n">
-        <v>0.00401</v>
-      </c>
-      <c r="L96" s="5" t="n">
-        <v>0.016642</v>
+      <c r="H96" s="5" t="n">
+        <v>0.027883</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Management fees and salaries (note 11)</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CHANGE IN CASH</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>0.127839</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>0.056718</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>-0.08895699999999999</v>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>0.005055</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -9965,124 +10001,148 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K97" s="5" t="n">
-        <v>0.094223</v>
-      </c>
-      <c r="L97" s="5" t="n">
-        <v>0.098301</v>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>CASH, BEGINNING OF YEAR</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E98" s="5" t="n">
-        <v>0.020398</v>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F98" s="5" t="n">
-        <v>0.089388</v>
+        <v>0.127839</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.044968</v>
+        <v>0.184557</v>
       </c>
       <c r="H98" s="5" t="n">
-        <v>0.035769</v>
-      </c>
-      <c r="I98" s="5" t="n">
-        <v>0.063177</v>
-      </c>
-      <c r="J98" s="5" t="n">
-        <v>0.071239</v>
-      </c>
-      <c r="K98" s="5" t="n">
-        <v>0.069327</v>
-      </c>
-      <c r="L98" s="5" t="n">
-        <v>0.056546</v>
+        <v>0.0956</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Transfer agent and regulatory</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CASH, END OF YEAR $</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="n">
+        <v>0.127839</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>0.184557</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>0.0956</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>0.013942</v>
-      </c>
-      <c r="I99" s="5" t="n">
-        <v>0.00603</v>
-      </c>
-      <c r="J99" s="5" t="n">
-        <v>0.026647</v>
-      </c>
-      <c r="K99" s="5" t="n">
-        <v>0.02658</v>
-      </c>
-      <c r="L99" s="5" t="n">
-        <v>0.022083</v>
+        <v>0.100655</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>SUPPLEMENTAL INFORMATION</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Stock-based compensation (note 9)</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
+          <t>Interest and income taxes paid $</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>IncomeTaxPaidSupplementalData</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -10103,42 +10163,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I100" s="5" t="n">
-        <v>0.9835</v>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K100" s="5" t="n">
-        <v>0.4148</v>
-      </c>
-      <c r="L100" s="5" t="n">
-        <v>0.27125</v>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>SUPPLEMENTAL INFORMATION</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Loss before other income</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Total $ 403,296 (65,990) 337,306 31,964</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -10149,15 +10211,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G101" s="5" t="n">
+        <v>0.315561</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>-0.053709</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -10169,34 +10227,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K101" s="5" t="n">
-        <v>7.403251</v>
-      </c>
-      <c r="L101" s="5" t="n">
-        <v>9.118506</v>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>SUPPLEMENTAL INFORMATION</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Deficit $ (360,420) (65,990) (426,410) -</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -10207,15 +10265,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G102" s="5" t="n">
+        <v>-0.480119</v>
+      </c>
+      <c r="H102" s="5" t="n">
+        <v>-0.053709</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -10227,27 +10281,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K102" s="5" t="n">
-        <v>-0.069105</v>
-      </c>
-      <c r="L102" s="5" t="n">
-        <v>-0.024142</v>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>$  -   -                                                                                                                                                                                                                      these</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Flow-through shares premium (notes 8 &amp; 12)</t>
+          <t>$  -   -                                                                                                                                                                                                                      these of Amount 553,645 553,645</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -10261,15 +10319,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G103" s="5" t="n">
+        <v>0.6044929999999999</v>
+      </c>
+      <c r="H103" s="5" t="n">
+        <v>0.050848</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -10281,43 +10335,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K103" s="5" t="n">
-        <v>-0.87125</v>
-      </c>
-      <c r="L103" s="5" t="n">
-        <v>-3.546687</v>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>$ LOSS AND COMPREHENSIVE LOSS FOR THE YEAR $</t>
+          <t>Exploration and evaluation asset</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>-0.046151</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>-0.100911</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -10339,43 +10393,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K104" s="5" t="n">
-        <v>-6.462896</v>
-      </c>
-      <c r="L104" s="5" t="n">
-        <v>-5.547677</v>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>LOSS PER SHARE (basic and diluted) $</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Payment of loan payable to related party</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F105" s="5" t="n">
+        <v>-0.012</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -10397,34 +10449,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K105" s="5" t="n">
-        <v>8e-08</v>
-      </c>
-      <c r="L105" s="5" t="n">
-        <v>5e-08</v>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding basic and diluted</t>
+          <t>Cash acquired on amalgamation with Pontiac Resources Corp.</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E106" s="5" t="n">
+        <v>0.000201</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10451,30 +10505,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K106" s="5" t="n">
-        <v>79.61559800000001</v>
-      </c>
-      <c r="L106" s="5" t="n">
-        <v>113.324389</v>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>SUPPLEMENTAL INFORMATION</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Balance, April 30, 2025 97,869,512 13,749,775 1,398,300 1,865,079</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
+          <t>Interest and income taxes paid</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>IncomeTaxPaidSupplementalData</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -10505,39 +10567,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K107" s="5" t="n">
-        <v>0.898273</v>
-      </c>
-      <c r="L107" s="5" t="n">
-        <v>-16.114881</v>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>SUPPLEMENTAL INFORMATION</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Issuance of common shares 44,125,000 9,000,000 - -</t>
+          <t>Total $ - 200,000 85,496 2,500 122,500 (146,244) 264,252 400,000 (115,446) 68,666</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E108" s="5" t="n">
+        <v>0.403296</v>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>-0.214176</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -10559,8 +10621,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K108" s="5" t="n">
-        <v>9</v>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -10571,29 +10635,25 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>SUPPLEMENTAL INFORMATION</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Issuance of warrants (257,500) - 257,500</t>
+          <t>Deficit $ - - - - - (146,244) (146,244) - - -</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E109" s="5" t="n">
+        <v>-0.36042</v>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>-0.214176</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -10629,29 +10689,25 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>of</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Issue costs - (59,542) - (3,356)</t>
+          <t>1 - - - - - part Common Shares integral of 4,000,000 2,000,000 2,500,000 8,500,001</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E110" s="5" t="n">
+        <v>12.500001</v>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -10673,8 +10729,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K110" s="5" t="n">
-        <v>-0.062898</v>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -10690,12 +10748,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Flow-through shares premium - (3,734,375) - -</t>
+          <t>Exploration expenses (notes 7, 11) $</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -10730,12 +10788,10 @@
         </is>
       </c>
       <c r="K111" s="5" t="n">
-        <v>-3.734375</v>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.783447</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>8.62969</v>
       </c>
     </row>
     <row r="112">
@@ -10746,15 +10802,19 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Expiry of warrants - - - (747,080)</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
+          <t>General administrative (note 11)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -10785,13 +10845,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K112" s="5" t="n">
+        <v>0.010864</v>
       </c>
       <c r="L112" s="5" t="n">
-        <v>0.74708</v>
+        <v>0.023994</v>
       </c>
     </row>
     <row r="113">
@@ -10802,12 +10860,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Issuance of stock options - - 271,250 -</t>
+          <t>Investor relations and promotion</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -10831,23 +10889,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I113" s="5" t="n">
+        <v>0.018635</v>
+      </c>
+      <c r="J113" s="5" t="n">
+        <v>0.038311</v>
       </c>
       <c r="K113" s="5" t="n">
-        <v>0.27125</v>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.00401</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>0.016642</v>
       </c>
     </row>
     <row r="114">
@@ -10858,12 +10910,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Exercise of stock options 445,000 64,525 (31,150) -</t>
+          <t>Management fees and salaries (note 11)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -10898,12 +10950,10 @@
         </is>
       </c>
       <c r="K114" s="5" t="n">
-        <v>0.033375</v>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.094223</v>
+      </c>
+      <c r="L114" s="5" t="n">
+        <v>0.098301</v>
       </c>
     </row>
     <row r="115">
@@ -10914,54 +10964,42 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Loss for the year - - - -</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="n">
+        <v>0.020398</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>0.089388</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>0.044968</v>
+      </c>
+      <c r="H115" s="5" t="n">
+        <v>0.035769</v>
+      </c>
+      <c r="I115" s="5" t="n">
+        <v>0.063177</v>
+      </c>
+      <c r="J115" s="5" t="n">
+        <v>0.071239</v>
       </c>
       <c r="K115" s="5" t="n">
-        <v>-5.547677</v>
+        <v>0.069327</v>
       </c>
       <c r="L115" s="5" t="n">
-        <v>-5.547677</v>
+        <v>0.056546</v>
       </c>
     </row>
     <row r="116">
@@ -10972,12 +11010,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Balance, April 30, 2026 142,439,512 18,762,883 1,638,400 1,372,143</t>
+          <t>Transfer agent and regulatory</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -10996,26 +11034,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H116" s="5" t="n">
+        <v>0.013942</v>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>0.00603</v>
+      </c>
+      <c r="J116" s="5" t="n">
+        <v>0.026647</v>
       </c>
       <c r="K116" s="5" t="n">
-        <v>0.857948</v>
+        <v>0.02658</v>
       </c>
       <c r="L116" s="5" t="n">
-        <v>-20.915478</v>
+        <v>0.022083</v>
       </c>
     </row>
     <row r="117">
@@ -11026,12 +11058,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Balance, April 30, 2024 53,137,369 8,832,378 1,177,365 985,052</t>
+          <t>Stock-based compensation (note 9)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -11055,10 +11087,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I117" s="5" t="n">
+        <v>0.9835</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -11066,10 +11096,10 @@
         </is>
       </c>
       <c r="K117" s="5" t="n">
-        <v>0.419158</v>
+        <v>0.4148</v>
       </c>
       <c r="L117" s="5" t="n">
-        <v>-10.575637</v>
+        <v>0.27125</v>
       </c>
     </row>
     <row r="118">
@@ -11080,15 +11110,19 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Issuance of common shares 44,732,143 7,100,000 - -</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr"/>
+          <t>Loss before other income</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -11120,12 +11154,10 @@
         </is>
       </c>
       <c r="K118" s="5" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.403251</v>
+      </c>
+      <c r="L118" s="5" t="n">
+        <v>9.118506</v>
       </c>
     </row>
     <row r="119">
@@ -11136,15 +11168,19 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Issuance of warrants - (1,642,280) - 1,642,280</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -11175,15 +11211,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K119" s="5" t="n">
+        <v>-0.069105</v>
+      </c>
+      <c r="L119" s="5" t="n">
+        <v>-0.024142</v>
       </c>
     </row>
     <row r="120">
@@ -11194,12 +11226,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Issue costs - (103,073) - (32,466)</t>
+          <t>Flow-through shares premium (notes 8 &amp; 12)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -11234,12 +11266,10 @@
         </is>
       </c>
       <c r="K120" s="5" t="n">
-        <v>-0.135539</v>
-      </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.87125</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>-3.546687</v>
       </c>
     </row>
     <row r="121">
@@ -11250,15 +11280,19 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Flow-through shares premium - (437,250) - -</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr"/>
+          <t>$ LOSS AND COMPREHENSIVE LOSS FOR THE YEAR $</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -11290,12 +11324,10 @@
         </is>
       </c>
       <c r="K121" s="5" t="n">
-        <v>-0.43725</v>
-      </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-6.462896</v>
+      </c>
+      <c r="L121" s="5" t="n">
+        <v>-5.547677</v>
       </c>
     </row>
     <row r="122">
@@ -11306,15 +11338,19 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Expiry of warrants - - - (729,787)</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr"/>
+          <t>LOSS PER SHARE (basic and diluted) $</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -11345,13 +11381,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K122" s="5" t="n">
+        <v>8e-08</v>
       </c>
       <c r="L122" s="5" t="n">
-        <v>0.729787</v>
+        <v>5e-08</v>
       </c>
     </row>
     <row r="123">
@@ -11362,12 +11396,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Issuance of stock options - - 414,800 -</t>
+          <t>Weighted average number of common shares outstanding basic and diluted</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -11402,12 +11436,10 @@
         </is>
       </c>
       <c r="K123" s="5" t="n">
-        <v>0.4148</v>
-      </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>79.61559800000001</v>
+      </c>
+      <c r="L123" s="5" t="n">
+        <v>113.324389</v>
       </c>
     </row>
     <row r="124">
@@ -11418,12 +11450,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Stock</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Expiry of stock options - - (193,865) -</t>
+          <t>Balance, April 30, 2025 97,869,512 13,749,775 1,398,300 1,865,079</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -11457,13 +11489,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K124" s="5" t="n">
+        <v>0.898273</v>
       </c>
       <c r="L124" s="5" t="n">
-        <v>0.193865</v>
+        <v>-16.114881</v>
       </c>
     </row>
     <row r="125">
@@ -11474,19 +11504,15 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Stock</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Loss for the year - - - -</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Issuance of common shares 44,125,000 9,000,000 - -</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -11518,10 +11544,12 @@
         </is>
       </c>
       <c r="K125" s="5" t="n">
-        <v>-6.462896</v>
-      </c>
-      <c r="L125" s="5" t="n">
-        <v>-6.462896</v>
+        <v>9</v>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="126">
@@ -11532,12 +11560,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Stock</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Balance, April 30, 2025 97,869,512 13,749,775 1,398,300 1,865,079</t>
+          <t>Issuance of warrants (257,500) - 257,500</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -11571,11 +11599,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K126" s="5" t="n">
-        <v>0.898273</v>
-      </c>
-      <c r="L126" s="5" t="n">
-        <v>-16.114881</v>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="127">
@@ -11584,10 +11616,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr"/>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>FOR THE YEARS ENDED APRIL</t>
+          <t>Issue costs - (59,542) - (3,356)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -11616,13 +11652,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J127" s="5" t="n">
-        <v>3e-05</v>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="n">
+        <v>-0.062898</v>
       </c>
       <c r="L127" t="inlineStr">
         <is>
@@ -11638,12 +11674,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Stock</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Exploration expenses (note 6) $ 6,783,447 $</t>
+          <t>Flow-through shares premium - (3,734,375) - -</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
@@ -11672,13 +11708,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J128" s="5" t="n">
-        <v>2.770067</v>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="n">
+        <v>-3.734375</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -11694,19 +11730,15 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Stock</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>General administrative 10,864</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Expiry of warrants - - - (747,080)</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -11732,18 +11764,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J129" s="5" t="n">
-        <v>0.014778</v>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L129" s="5" t="n">
+        <v>0.74708</v>
       </c>
     </row>
     <row r="130">
@@ -11754,12 +11786,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Stock</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Investor relations and promotion 4,010</t>
+          <t>Issuance of stock options - - 271,250 -</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -11788,13 +11820,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J130" s="5" t="n">
-        <v>0.038311</v>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="n">
+        <v>0.27125</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -11810,12 +11842,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Stock</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Management fees and salaries (note 10) 94,223</t>
+          <t>Exercise of stock options 445,000 64,525 (31,150) -</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -11844,13 +11876,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J131" s="5" t="n">
-        <v>0.093719</v>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="n">
+        <v>0.033375</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -11866,17 +11898,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Stock</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Professional fees (note 10) 69,327</t>
+          <t>Loss for the year - - - -</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -11904,18 +11936,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J132" s="5" t="n">
-        <v>0.071239</v>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="n">
+        <v>-5.547677</v>
+      </c>
+      <c r="L132" s="5" t="n">
+        <v>-5.547677</v>
       </c>
     </row>
     <row r="133">
@@ -11926,12 +11956,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Stock</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Transfer agent and regulatory 26,580</t>
+          <t>Balance, April 30, 2026 142,439,512 18,762,883 1,638,400 1,372,143</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -11960,18 +11990,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J133" s="5" t="n">
-        <v>0.026647</v>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>0.857948</v>
+      </c>
+      <c r="L133" s="5" t="n">
+        <v>-20.915478</v>
       </c>
     </row>
     <row r="134">
@@ -11982,12 +12010,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Stock-based compensation (note 8) 414,800</t>
+          <t>Balance, April 30, 2024 53,137,369 8,832,378 1,177,365 985,052</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -12021,15 +12049,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K134" s="5" t="n">
+        <v>0.419158</v>
+      </c>
+      <c r="L134" s="5" t="n">
+        <v>-10.575637</v>
       </c>
     </row>
     <row r="135">
@@ -12040,19 +12064,15 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Loss before other income 7,403,251</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Issuance of common shares 44,732,143 7,100,000 - -</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -12078,13 +12098,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J135" s="5" t="n">
-        <v>3.014761</v>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="n">
+        <v>7.1</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -12100,12 +12120,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Other income expense</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Interest income (69,105)</t>
+          <t>Issuance of warrants - (1,642,280) - 1,642,280</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -12134,8 +12154,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J136" s="5" t="n">
-        <v>-0.053395</v>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
@@ -12156,12 +12178,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Other income expense</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Flow-through shares premium (notes 7 &amp; 11) (871,250)</t>
+          <t>Issue costs - (103,073) - (32,466)</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
@@ -12190,13 +12212,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J137" s="5" t="n">
-        <v>-0.554491</v>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="n">
+        <v>-0.135539</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -12212,19 +12234,15 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Other income expense</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>$ LOSS AND COMPREHENSIVE LOSS FOR THE YEAR $ 6,462,896</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Flow-through shares premium - (437,250) - -</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -12250,13 +12268,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J138" s="5" t="n">
-        <v>-2.406875</v>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="n">
+        <v>-0.43725</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -12272,12 +12290,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Other income expense</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>LOSS PER SHARE (basic and diluted) $ 0.08 $</t>
+          <t>Expiry of warrants - - - (729,787)</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
@@ -12306,18 +12324,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J139" s="5" t="n">
-        <v>5e-08</v>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L139" s="5" t="n">
+        <v>0.729787</v>
       </c>
     </row>
     <row r="140">
@@ -12328,12 +12346,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Other income expense</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding basic and diluted 79,615,598</t>
+          <t>Issuance of stock options - - 414,800 -</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
@@ -12362,13 +12380,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J140" s="5" t="n">
-        <v>51.637369</v>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>0.4148</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -12389,7 +12407,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Balance, April 30, 2024 53,137,369 8,832,378 1,177,365 985,052 (10,575,637)</t>
+          <t>Expiry of stock options - - (193,865) -</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
@@ -12418,18 +12436,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J141" s="5" t="n">
-        <v>0.419158</v>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L141" s="5" t="n">
+        <v>0.193865</v>
       </c>
     </row>
     <row r="142">
@@ -12445,10 +12463,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Issuance of common shares 44,732,143 7,100,000 - - -</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr"/>
+          <t>Loss for the year - - - -</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -12474,18 +12496,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J142" s="5" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="n">
+        <v>-6.462896</v>
+      </c>
+      <c r="L142" s="5" t="n">
+        <v>-6.462896</v>
       </c>
     </row>
     <row r="143">
@@ -12501,7 +12521,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Issuance of warrants (1,642,280) - 1,642,280 -</t>
+          <t>Balance, April 30, 2025 97,869,512 13,749,775 1,398,300 1,865,079</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -12535,15 +12555,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K143" s="5" t="n">
+        <v>0.898273</v>
+      </c>
+      <c r="L143" s="5" t="n">
+        <v>-16.114881</v>
       </c>
     </row>
     <row r="144">
@@ -12552,14 +12568,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Shares</t>
-        </is>
-      </c>
+      <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Issue costs - cash - (103,073) - (32,466) -</t>
+          <t>FOR THE YEARS ENDED APRIL</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -12589,7 +12601,7 @@
         </is>
       </c>
       <c r="J144" s="5" t="n">
-        <v>-0.135539</v>
+        <v>3e-05</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
@@ -12610,12 +12622,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Flow-through shares premium - (437,250) - - -</t>
+          <t>Exploration expenses (note 6) $ 6,783,447 $</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -12645,7 +12657,7 @@
         </is>
       </c>
       <c r="J145" s="5" t="n">
-        <v>-0.43725</v>
+        <v>2.770067</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
@@ -12666,15 +12678,19 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Issuance of stock options - - 414,800 - -</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr"/>
+          <t>General administrative 10,864</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -12701,7 +12717,7 @@
         </is>
       </c>
       <c r="J146" s="5" t="n">
-        <v>0.4148</v>
+        <v>0.014778</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -12722,12 +12738,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Expiry of stock options - - (193,865) 193,865</t>
+          <t>Investor relations and promotion 4,010</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -12756,10 +12772,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J147" s="5" t="n">
+        <v>0.038311</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
@@ -12780,12 +12794,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Expiry of warrants - - - (729,787) 729,787</t>
+          <t>Management fees and salaries (note 10) 94,223</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -12814,10 +12828,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J148" s="5" t="n">
+        <v>0.093719</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
@@ -12838,15 +12850,19 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Loss for the year - - - - (6,462,896)</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr"/>
+          <t>Professional fees (note 10) 69,327</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -12873,7 +12889,7 @@
         </is>
       </c>
       <c r="J149" s="5" t="n">
-        <v>-6.462896</v>
+        <v>0.071239</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
@@ -12894,12 +12910,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Balance, April 30, 2025 97,869,512 13,749,775 1,398,300 1,865,079 (16,114,881)</t>
+          <t>Transfer agent and regulatory 26,580</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -12929,7 +12945,7 @@
         </is>
       </c>
       <c r="J150" s="5" t="n">
-        <v>0.898273</v>
+        <v>0.026647</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
@@ -12950,12 +12966,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Balance, April 30, 2023 46,137,369 7,733,924 1,177,365 729,787 (8,168,762)</t>
+          <t>Stock-based compensation (note 8) 414,800</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -12984,8 +13000,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J151" s="5" t="n">
-        <v>1.472314</v>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
@@ -13006,15 +13024,19 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Issuance of common shares 7,000,000 2,250,000 - - -</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
+          <t>Loss before other income 7,403,251</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -13035,11 +13057,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I152" s="5" t="n">
-        <v>2.25</v>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J152" s="5" t="n">
-        <v>2.25</v>
+        <v>3.014761</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
@@ -13060,12 +13084,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Other income expense</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Issuance of warrants - (260,000) - 260,000 -</t>
+          <t>Interest income (69,105)</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -13094,10 +13118,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J153" s="5" t="n">
+        <v>-0.053395</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
@@ -13118,12 +13140,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Other income expense</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Issue costs - (21,546) - (4,735) -</t>
+          <t>Flow-through shares premium (notes 7 &amp; 11) (871,250)</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -13153,7 +13175,7 @@
         </is>
       </c>
       <c r="J154" s="5" t="n">
-        <v>-0.026281</v>
+        <v>-0.554491</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
@@ -13174,15 +13196,19 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Other income expense</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Flow-through shares premium - (870,000) - - -</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr"/>
+          <t>$ LOSS AND COMPREHENSIVE LOSS FOR THE YEAR $ 6,462,896</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -13203,11 +13229,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I155" s="5" t="n">
-        <v>-0.87</v>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J155" s="5" t="n">
-        <v>-0.87</v>
+        <v>-2.406875</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
@@ -13228,12 +13256,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Other income expense</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Loss for the year - - - (2,406,875)</t>
+          <t>LOSS PER SHARE (basic and diluted) $ 0.08 $</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -13263,7 +13291,7 @@
         </is>
       </c>
       <c r="J156" s="5" t="n">
-        <v>-2.406875</v>
+        <v>5e-08</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -13284,12 +13312,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Other income expense</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Exploration expenses (note 7) $</t>
+          <t>Weighted average number of common shares outstanding basic and diluted 79,615,598</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -13313,11 +13341,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I157" s="5" t="n">
-        <v>1.721355</v>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J157" s="5" t="n">
-        <v>2.770067</v>
+        <v>51.637369</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
@@ -13338,19 +13368,15 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>General administrative</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Balance, April 30, 2024 53,137,369 8,832,378 1,177,365 985,052 (10,575,637)</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -13366,14 +13392,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H158" s="5" t="n">
-        <v>0.000217</v>
-      </c>
-      <c r="I158" s="5" t="n">
-        <v>0.11935</v>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J158" s="5" t="n">
-        <v>0.014778</v>
+        <v>0.419158</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
@@ -13394,12 +13424,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Management fees and salaries</t>
+          <t>Issuance of common shares 44,732,143 7,100,000 - - -</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -13423,11 +13453,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I159" s="5" t="n">
-        <v>0.183662</v>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J159" s="5" t="n">
-        <v>0.093719</v>
+        <v>7.1</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
@@ -13448,19 +13480,15 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Loss before other (income) expense</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Issuance of warrants (1,642,280) - 1,642,280 -</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -13481,11 +13509,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I160" s="5" t="n">
-        <v>3.095709</v>
-      </c>
-      <c r="J160" s="5" t="n">
-        <v>3.014761</v>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
@@ -13506,19 +13538,15 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Other (income) expense</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Issue costs - cash - (103,073) - (32,466) -</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -13539,11 +13567,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I161" s="5" t="n">
-        <v>-0.032593</v>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J161" s="5" t="n">
-        <v>-0.053395</v>
+        <v>-0.135539</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
@@ -13564,12 +13594,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Other (income) expense</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Flow-through shares premium (note 12)</t>
+          <t>Flow-through shares premium - (437,250) - - -</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -13593,11 +13623,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I162" s="5" t="n">
-        <v>-0.171609</v>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J162" s="5" t="n">
-        <v>-0.554491</v>
+        <v>-0.43725</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
@@ -13618,12 +13650,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Other (income) expense</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Listing expenses (note 2)</t>
+          <t>Issuance of stock options - - 414,800 - -</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -13647,13 +13679,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I163" s="5" t="n">
-        <v>5.201969</v>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J163" s="5" t="n">
+        <v>0.4148</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
@@ -13674,19 +13706,15 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Other (income) expense</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>$ LOSS AND COMPREHENSIVE LOSS FOR THE YEAR $</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Expiry of stock options - - (193,865) 193,865</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -13707,11 +13735,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I164" s="5" t="n">
-        <v>-8.093476000000001</v>
-      </c>
-      <c r="J164" s="5" t="n">
-        <v>-2.406875</v>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
@@ -13732,19 +13764,15 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Other (income) expense</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>LOSS PER SHARE (basic and diluted) $</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Expiry of warrants - - - (729,787) 729,787</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -13765,11 +13793,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I165" s="5" t="n">
-        <v>2.5e-07</v>
-      </c>
-      <c r="J165" s="5" t="n">
-        <v>5e-08</v>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
@@ -13790,12 +13822,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding basic</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding basic and diluted</t>
+          <t>Loss for the year - - - - (6,462,896)</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
@@ -13819,11 +13851,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I166" s="5" t="n">
-        <v>32.490701</v>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J166" s="5" t="n">
-        <v>51.637369</v>
+        <v>-6.462896</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
@@ -13849,7 +13883,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Balances, April 30, 2023 46,137,369 7,733,924 - 1,177,365 729,787</t>
+          <t>Balance, April 30, 2025 97,869,512 13,749,775 1,398,300 1,865,079 (16,114,881)</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -13873,11 +13907,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I167" s="5" t="n">
-        <v>1.472314</v>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J167" s="5" t="n">
-        <v>-8.168761999999999</v>
+        <v>0.898273</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
@@ -13903,7 +13939,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Issue costs - (21,546) - - (4,735)</t>
+          <t>Balance, April 30, 2023 46,137,369 7,733,924 1,177,365 729,787 (8,168,762)</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
@@ -13927,13 +13963,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I168" s="5" t="n">
-        <v>-0.026281</v>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J168" s="5" t="n">
+        <v>1.472314</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
@@ -13959,7 +13995,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Issuance of warrants - (260,000) - - 260,000</t>
+          <t>Issuance of common shares 7,000,000 2,250,000 - - -</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -13983,15 +14019,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I169" s="5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J169" s="5" t="n">
+        <v>2.25</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -14012,19 +14044,15 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year - - - - -</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Issuance of warrants - (260,000) - 260,000 -</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -14045,11 +14073,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I170" s="5" t="n">
-        <v>-2.406875</v>
-      </c>
-      <c r="J170" s="5" t="n">
-        <v>-2.406875</v>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -14070,12 +14102,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Balance, April 30, 2024 53,137,369 8,832,378 - 1,177,365 985,052</t>
+          <t>Issue costs - (21,546) - (4,735) -</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -14099,11 +14131,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I171" s="5" t="n">
-        <v>0.419158</v>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J171" s="5" t="n">
-        <v>-10.575637</v>
+        <v>-0.026281</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -14124,12 +14158,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Balances, April 30, 2022 Restated</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>(note 2) - - 75,286 - -</t>
+          <t>Flow-through shares premium - (870,000) - - -</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
@@ -14153,13 +14187,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I172" s="5" t="n">
+        <v>-0.87</v>
       </c>
       <c r="J172" s="5" t="n">
-        <v>-0.07528600000000001</v>
+        <v>-0.87</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -14180,12 +14212,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Balances, April 30, 2022 Restated</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Investment by Parent in the year - - 467,647 - -</t>
+          <t>Loss for the year - - - (2,406,875)</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -14209,13 +14241,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I173" s="5" t="n">
-        <v>0.467647</v>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J173" s="5" t="n">
+        <v>-2.406875</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
@@ -14236,12 +14268,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Shares issued to KLS Project</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Shares issued to KLS Project shareholders 25,639,288 542,933 (542,933) - -</t>
+          <t>Exploration expenses (note 7) $</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -14265,15 +14297,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I174" s="5" t="n">
+        <v>1.721355</v>
+      </c>
+      <c r="J174" s="5" t="n">
+        <v>2.770067</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
@@ -14294,15 +14322,19 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Consideration issued in arrangement</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Consideration issued in arrangement to Abasca shareholders 12,819,644 4,577,978 - 193,865 -</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
+          <t>General administrative</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -14318,18 +14350,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H175" s="5" t="n">
+        <v>0.000217</v>
       </c>
       <c r="I175" s="5" t="n">
-        <v>4.771843</v>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.11935</v>
+      </c>
+      <c r="J175" s="5" t="n">
+        <v>0.014778</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
@@ -14350,12 +14378,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Consideration issued in arrangement</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Issuance of common shares 7,678,437 3,745,212 - - -</t>
+          <t>Management fees and salaries</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -14380,12 +14408,10 @@
         </is>
       </c>
       <c r="I176" s="5" t="n">
-        <v>3.745212</v>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.183662</v>
+      </c>
+      <c r="J176" s="5" t="n">
+        <v>0.093719</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
@@ -14406,15 +14432,19 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Consideration issued in arrangement</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Issue costs - cash - (92,790) - - (19,522)</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
+          <t>Loss before other (income) expense</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -14436,12 +14466,10 @@
         </is>
       </c>
       <c r="I177" s="5" t="n">
-        <v>-0.112312</v>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.095709</v>
+      </c>
+      <c r="J177" s="5" t="n">
+        <v>3.014761</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
@@ -14462,15 +14490,19 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Consideration issued in arrangement</t>
+          <t>Other (income) expense</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Issue costs - Finders warrants - (36,001) - - 36,001</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -14491,15 +14523,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I178" s="5" t="n">
+        <v>-0.032593</v>
+      </c>
+      <c r="J178" s="5" t="n">
+        <v>-0.053395</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
@@ -14520,12 +14548,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Consideration issued in arrangement</t>
+          <t>Other (income) expense</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Flow-through shares premium - (290,100) - - -</t>
+          <t>Flow-through shares premium (note 12)</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -14550,12 +14578,10 @@
         </is>
       </c>
       <c r="I179" s="5" t="n">
-        <v>-0.2901</v>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.171609</v>
+      </c>
+      <c r="J179" s="5" t="n">
+        <v>-0.554491</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
@@ -14576,12 +14602,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Consideration issued in arrangement</t>
+          <t>Other (income) expense</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Issuance of warrants - (713,308) - - 713,308</t>
+          <t>Listing expenses (note 2)</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -14605,10 +14631,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I180" s="5" t="n">
+        <v>5.201969</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
@@ -14634,15 +14658,19 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Consideration issued in arrangement</t>
+          <t>Other (income) expense</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Issuance of stock options - - - 983,500 -</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
+          <t>$ LOSS AND COMPREHENSIVE LOSS FOR THE YEAR $</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -14664,12 +14692,10 @@
         </is>
       </c>
       <c r="I181" s="5" t="n">
-        <v>0.9835</v>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-8.093476000000001</v>
+      </c>
+      <c r="J181" s="5" t="n">
+        <v>-2.406875</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
@@ -14690,15 +14716,19 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Balance, April 30, 2023 - Restated</t>
+          <t>Other (income) expense</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>(note 2) 46,137,369 7,733,924 - 1,177,365 729,787</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
+          <t>LOSS PER SHARE (basic and diluted) $</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -14720,10 +14750,10 @@
         </is>
       </c>
       <c r="I182" s="5" t="n">
-        <v>1.472314</v>
+        <v>2.5e-07</v>
       </c>
       <c r="J182" s="5" t="n">
-        <v>-8.168761999999999</v>
+        <v>5e-08</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
@@ -14744,12 +14774,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Weighted average number of common shares outstanding basic</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Exploration expenses (Note 7) $</t>
+          <t>Weighted average number of common shares outstanding basic and diluted</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
@@ -14774,12 +14804,10 @@
         </is>
       </c>
       <c r="I183" s="5" t="n">
-        <v>4.285284</v>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>32.490701</v>
+      </c>
+      <c r="J183" s="5" t="n">
+        <v>51.637369</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
@@ -14800,12 +14828,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Management fees and salaries (Note 11)</t>
+          <t>Balances, April 30, 2023 46,137,369 7,733,924 - 1,177,365 729,787</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
@@ -14830,12 +14858,10 @@
         </is>
       </c>
       <c r="I184" s="5" t="n">
-        <v>0.034532</v>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.472314</v>
+      </c>
+      <c r="J184" s="5" t="n">
+        <v>-8.168761999999999</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
@@ -14856,19 +14882,15 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Professional fees (Note 11)</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Issue costs - (21,546) - - (4,735)</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -14884,11 +14906,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H185" s="5" t="n">
-        <v>0.035769</v>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I185" s="5" t="n">
-        <v>0.095999</v>
+        <v>-0.026281</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
@@ -14914,12 +14938,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>RTO expenses (Notes 1, 11)</t>
+          <t>Issuance of warrants - (260,000) - - 260,000</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -14943,8 +14967,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I186" s="5" t="n">
-        <v>0.276744</v>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
@@ -14970,15 +14996,19 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Loss and comprehensive loss for the</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Stock-based compensation (Note 9)</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
+          <t>Loss and comprehensive loss for the year - - - - -</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -14994,16 +15024,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H187" s="5" t="n">
-        <v>0.003781</v>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I187" s="5" t="n">
-        <v>0.9835</v>
-      </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.406875</v>
+      </c>
+      <c r="J187" s="5" t="n">
+        <v>-2.406875</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
@@ -15024,19 +15054,15 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Loss and comprehensive loss for the</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Loss before other items</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Balance, April 30, 2024 53,137,369 8,832,378 - 1,177,365 985,052</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -15052,16 +15078,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H188" s="5" t="n">
-        <v>0.053709</v>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I188" s="5" t="n">
-        <v>5.719413</v>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.419158</v>
+      </c>
+      <c r="J188" s="5" t="n">
+        <v>-10.575637</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
@@ -15082,19 +15108,15 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Balances, April 30, 2022 Restated</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>(note 2) - - 75,286 - -</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -15115,13 +15137,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I189" s="5" t="n">
-        <v>-0.032593</v>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J189" s="5" t="n">
+        <v>-0.07528600000000001</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
@@ -15142,12 +15164,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Balances, April 30, 2022 Restated</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Mining exploration tax credits</t>
+          <t>Investment by Parent in the year - - 467,647 - -</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -15166,13 +15188,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H190" s="5" t="n">
-        <v>-0.027883</v>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I190" s="5" t="n">
+        <v>0.467647</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
@@ -15198,12 +15220,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shares issued to KLS Project</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Flow-through shares premium (Notes 8, 12)</t>
+          <t>Shares issued to KLS Project shareholders 25,639,288 542,933 (542,933) - -</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -15227,8 +15249,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I191" s="5" t="n">
-        <v>-0.171609</v>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
@@ -15254,19 +15278,15 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Consideration issued in arrangement</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>$ LOSS AND COMPREHENSIVE LOSS FOR THE YEAR $</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Consideration issued in arrangement to Abasca shareholders 12,819,644 4,577,978 - 193,865 -</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -15282,11 +15302,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H192" s="5" t="n">
-        <v>-0.025826</v>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I192" s="5" t="n">
-        <v>-5.515211</v>
+        <v>4.771843</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
@@ -15312,19 +15334,15 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Consideration issued in arrangement</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>LOSS PER SHARE (basic and diluted) $</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Issuance of common shares 7,678,437 3,745,212 - - -</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -15340,11 +15358,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H193" s="5" t="n">
-        <v>0</v>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I193" s="5" t="n">
-        <v>2.3e-07</v>
+        <v>3.745212</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -15370,19 +15390,15 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Consideration issued in arrangement</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Issue costs - cash - (92,790) - - (19,522)</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -15398,11 +15414,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H194" s="5" t="n">
-        <v>12.624355</v>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I194" s="5" t="n">
-        <v>23.95598</v>
+        <v>-0.112312</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
@@ -15428,30 +15446,34 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Consideration issued in arrangement</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Office $</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E195" s="5" t="n">
-        <v>0.000346</v>
-      </c>
-      <c r="F195" s="5" t="n">
-        <v>0.001874</v>
-      </c>
-      <c r="G195" s="5" t="n">
-        <v>0.000215</v>
-      </c>
-      <c r="H195" s="5" t="n">
-        <v>0.000217</v>
+          <t>Issue costs - Finders warrants - (36,001) - - 36,001</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
@@ -15482,12 +15504,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Consideration issued in arrangement</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Prospect evaluation</t>
+          <t>Flow-through shares premium - (290,100) - - -</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
@@ -15501,18 +15523,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G196" s="5" t="n">
-        <v>0.006085</v>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I196" s="5" t="n">
+        <v>-0.2901</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
@@ -15538,32 +15560,34 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Consideration issued in arrangement</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Issuance of warrants - (713,308) - - 713,308</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F197" s="5" t="n">
-        <v>0.043121</v>
-      </c>
-      <c r="G197" s="5" t="n">
-        <v>0.014722</v>
-      </c>
-      <c r="H197" s="5" t="n">
-        <v>0.013942</v>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
@@ -15594,39 +15618,37 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Consideration issued in arrangement</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Travel</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Issuance of stock options - - - 983,500 -</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F198" s="5" t="n">
-        <v>0.011127</v>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H198" s="5" t="n">
-        <v>0.003781</v>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I198" s="5" t="n">
+        <v>0.9835</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
@@ -15652,40 +15674,40 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Balance, April 30, 2023 - Restated</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>NET LOSS AND COMPREHENSIVE LOSS $</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E199" s="5" t="n">
-        <v>-0.146244</v>
-      </c>
-      <c r="F199" s="5" t="n">
-        <v>-0.214176</v>
-      </c>
-      <c r="G199" s="5" t="n">
-        <v>-0.06598999999999999</v>
-      </c>
-      <c r="H199" s="5" t="n">
-        <v>-0.053709</v>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>(note 2) 46,137,369 7,733,924 - 1,177,365 729,787</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I199" s="5" t="n">
+        <v>1.472314</v>
+      </c>
+      <c r="J199" s="5" t="n">
+        <v>-8.168761999999999</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
@@ -15711,30 +15733,32 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>LOSS PER SHARE – BASIC AND DILUTED $</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E200" s="5" t="n">
-        <v>-4e-08</v>
-      </c>
-      <c r="F200" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="G200" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="H200" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Exploration expenses (Note 7) $</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I200" s="5" t="n">
+        <v>4.285284</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
@@ -15760,12 +15784,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>WEIGHTED AVERAGE NUMBER OF COMMON SHARES</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>OUTSTANDING</t>
+          <t>Management fees and salaries (Note 11)</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
@@ -15774,19 +15798,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F201" s="5" t="n">
-        <v>10.034248</v>
-      </c>
-      <c r="G201" s="5" t="n">
-        <v>12.500001</v>
-      </c>
-      <c r="H201" s="5" t="n">
-        <v>12.624355</v>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I201" s="5" t="n">
+        <v>0.034532</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
@@ -15817,30 +15845,34 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Share-based payments (Note 7)</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr"/>
-      <c r="E202" s="5" t="n">
-        <v>0.1225</v>
-      </c>
-      <c r="F202" s="5" t="n">
-        <v>0.068666</v>
+          <t>Professional fees (Note 11)</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H202" s="5" t="n">
+        <v>0.035769</v>
+      </c>
+      <c r="I202" s="5" t="n">
+        <v>0.095999</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
@@ -15871,16 +15903,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Rent</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E203" s="5" t="n">
-        <v>0.003</v>
+          <t>RTO expenses (Notes 1, 11)</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15897,10 +15927,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I203" s="5" t="n">
+        <v>0.276744</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
@@ -15931,46 +15959,1002 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
+          <t>Stock-based compensation (Note 9)</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H204" s="5" t="n">
+        <v>0.003781</v>
+      </c>
+      <c r="I204" s="5" t="n">
+        <v>0.9835</v>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Loss before other items</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H205" s="5" t="n">
+        <v>0.053709</v>
+      </c>
+      <c r="I205" s="5" t="n">
+        <v>5.719413</v>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I206" s="5" t="n">
+        <v>-0.032593</v>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Mining exploration tax credits</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H207" s="5" t="n">
+        <v>-0.027883</v>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Flow-through shares premium (Notes 8, 12)</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I208" s="5" t="n">
+        <v>-0.171609</v>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>$ LOSS AND COMPREHENSIVE LOSS FOR THE YEAR $</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H209" s="5" t="n">
+        <v>-0.025826</v>
+      </c>
+      <c r="I209" s="5" t="n">
+        <v>-5.515211</v>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>LOSS PER SHARE (basic and diluted) $</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H210" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I210" s="5" t="n">
+        <v>2.3e-07</v>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H211" s="5" t="n">
+        <v>12.624355</v>
+      </c>
+      <c r="I211" s="5" t="n">
+        <v>23.95598</v>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Office $</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E212" s="5" t="n">
+        <v>0.000346</v>
+      </c>
+      <c r="F212" s="5" t="n">
+        <v>0.001874</v>
+      </c>
+      <c r="G212" s="5" t="n">
+        <v>0.000215</v>
+      </c>
+      <c r="H212" s="5" t="n">
+        <v>0.000217</v>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Prospect evaluation</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G213" s="5" t="n">
+        <v>0.006085</v>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Transfer agent and filing fees</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F214" s="5" t="n">
+        <v>0.043121</v>
+      </c>
+      <c r="G214" s="5" t="n">
+        <v>0.014722</v>
+      </c>
+      <c r="H214" s="5" t="n">
+        <v>0.013942</v>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F215" s="5" t="n">
+        <v>0.011127</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H215" s="5" t="n">
+        <v>0.003781</v>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>NET LOSS AND COMPREHENSIVE LOSS $</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E216" s="5" t="n">
+        <v>-0.146244</v>
+      </c>
+      <c r="F216" s="5" t="n">
+        <v>-0.214176</v>
+      </c>
+      <c r="G216" s="5" t="n">
+        <v>-0.06598999999999999</v>
+      </c>
+      <c r="H216" s="5" t="n">
+        <v>-0.053709</v>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>LOSS PER SHARE – BASIC AND DILUTED $</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E217" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="F217" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="G217" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="H217" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>WEIGHTED AVERAGE NUMBER OF COMMON SHARES</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>OUTSTANDING</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F218" s="5" t="n">
+        <v>10.034248</v>
+      </c>
+      <c r="G218" s="5" t="n">
+        <v>12.500001</v>
+      </c>
+      <c r="H218" s="5" t="n">
+        <v>12.624355</v>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Share-based payments (Note 7)</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" s="5" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="F219" s="5" t="n">
+        <v>0.068666</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E220" s="5" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
           <t>WEIGHTED AVERAGE NUMBER OF COMMON SHARES OUTSTANDING</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr">
+      <c r="D221" t="inlineStr">
         <is>
           <t>SharesOutstanding</t>
         </is>
       </c>
-      <c r="E204" s="5" t="n">
+      <c r="E221" s="5" t="n">
         <v>4.143014</v>
       </c>
-      <c r="F204" s="5" t="n">
+      <c r="F221" s="5" t="n">
         <v>10.034248</v>
       </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L204" t="inlineStr">
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
         <is>
           <t>-</t>
         </is>
